--- a/artfynd/A 33612-2020 artfynd.xlsx
+++ b/artfynd/A 33612-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33612-2020 artfynd.xlsx
+++ b/artfynd/A 33612-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118478696</v>
+        <v>118478514</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,41 +816,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586054</v>
+        <v>586052</v>
       </c>
       <c r="R3" t="n">
-        <v>7060060</v>
+        <v>7060071</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,9 +882,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +909,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118478727</v>
+        <v>118478591</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,31 +933,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586054</v>
+        <v>586053</v>
       </c>
       <c r="R4" t="n">
-        <v>7060060</v>
+        <v>7060067</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,9 +999,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +1026,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118478567</v>
+        <v>118478345</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,42 +1054,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586043</v>
+        <v>585999</v>
       </c>
       <c r="R5" t="n">
-        <v>7060090</v>
+        <v>7060119</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,9 +1111,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1138,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118478345</v>
+        <v>118478669</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585999</v>
+        <v>586054</v>
       </c>
       <c r="R6" t="n">
-        <v>7060119</v>
+        <v>7060060</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,19 +1223,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118478591</v>
+        <v>118478727</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>56502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,31 +1264,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1277,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586053</v>
+        <v>586054</v>
       </c>
       <c r="R7" t="n">
-        <v>7060067</v>
+        <v>7060060</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,19 +1330,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,19 +1347,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118478514</v>
+        <v>118478567</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1394,13 +1404,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586052</v>
+        <v>586043</v>
       </c>
       <c r="R8" t="n">
-        <v>7060071</v>
+        <v>7060090</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,19 +1437,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,12 +1454,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 33612-2020 artfynd.xlsx
+++ b/artfynd/A 33612-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118478514</v>
+        <v>118478591</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586052</v>
+        <v>586053</v>
       </c>
       <c r="R3" t="n">
-        <v>7060071</v>
+        <v>7060067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118478591</v>
+        <v>118478727</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>56502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +933,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586053</v>
+        <v>586054</v>
       </c>
       <c r="R4" t="n">
-        <v>7060067</v>
+        <v>7060060</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,19 +999,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,22 +1016,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118478345</v>
+        <v>118478514</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,34 +1044,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585999</v>
+        <v>586052</v>
       </c>
       <c r="R5" t="n">
-        <v>7060119</v>
+        <v>7060071</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118478669</v>
+        <v>118478567</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1157,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586054</v>
+        <v>586043</v>
       </c>
       <c r="R6" t="n">
-        <v>7060060</v>
+        <v>7060090</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118478727</v>
+        <v>118478345</v>
       </c>
       <c r="B7" t="n">
-        <v>56502</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,46 +1264,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586054</v>
+        <v>585999</v>
       </c>
       <c r="R7" t="n">
-        <v>7060060</v>
+        <v>7060119</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,9 +1325,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118478567</v>
+        <v>118478669</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>91779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,43 +1376,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586043</v>
+        <v>586054</v>
       </c>
       <c r="R8" t="n">
-        <v>7060090</v>
+        <v>7060060</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 33612-2020 artfynd.xlsx
+++ b/artfynd/A 33612-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118478591</v>
+        <v>118478514</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586053</v>
+        <v>586052</v>
       </c>
       <c r="R3" t="n">
-        <v>7060067</v>
+        <v>7060071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118478727</v>
+        <v>118478591</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +933,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586054</v>
+        <v>586053</v>
       </c>
       <c r="R4" t="n">
-        <v>7060060</v>
+        <v>7060067</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,9 +999,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,22 +1026,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118478514</v>
+        <v>118478696</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>91786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,46 +1050,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586052</v>
+        <v>586054</v>
       </c>
       <c r="R5" t="n">
-        <v>7060071</v>
+        <v>7060060</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,19 +1111,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118478567</v>
+        <v>118478345</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,42 +1156,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586043</v>
+        <v>585999</v>
       </c>
       <c r="R6" t="n">
-        <v>7060090</v>
+        <v>7060119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,9 +1213,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118478345</v>
+        <v>118478727</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>56502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,41 +1264,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585999</v>
+        <v>586054</v>
       </c>
       <c r="R7" t="n">
-        <v>7060119</v>
+        <v>7060060</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,19 +1330,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118478669</v>
+        <v>118478567</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,38 +1371,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586054</v>
+        <v>586043</v>
       </c>
       <c r="R8" t="n">
-        <v>7060060</v>
+        <v>7060090</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 33612-2020 artfynd.xlsx
+++ b/artfynd/A 33612-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118478514</v>
+        <v>118478727</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>56502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,31 +816,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586052</v>
+        <v>586054</v>
       </c>
       <c r="R3" t="n">
-        <v>7060071</v>
+        <v>7060060</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,19 +882,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,22 +899,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118478591</v>
+        <v>118478345</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,39 +927,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586053</v>
+        <v>585999</v>
       </c>
       <c r="R4" t="n">
-        <v>7060067</v>
+        <v>7060119</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118478696</v>
+        <v>118478660</v>
       </c>
       <c r="B5" t="n">
         <v>91786</v>
@@ -1140,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118478345</v>
+        <v>118478567</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,37 +1141,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585999</v>
+        <v>586043</v>
       </c>
       <c r="R6" t="n">
-        <v>7060119</v>
+        <v>7060090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,19 +1203,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118478727</v>
+        <v>118478591</v>
       </c>
       <c r="B7" t="n">
-        <v>56502</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,31 +1244,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586054</v>
+        <v>586053</v>
       </c>
       <c r="R7" t="n">
-        <v>7060060</v>
+        <v>7060067</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,9 +1310,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1337,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118478567</v>
+        <v>118478514</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1404,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586043</v>
+        <v>586052</v>
       </c>
       <c r="R8" t="n">
-        <v>7060090</v>
+        <v>7060071</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,9 +1427,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,12 +1454,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
